--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B2" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R2" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R3" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R2" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R3" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B2" t="n">
-        <v>92021</v>
+        <v>92030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R2" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>92030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R3" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B2" t="n">
         <v>92055</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R2" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B3" t="n">
         <v>92055</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R3" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B2" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R2" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R3" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031523</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122031485</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56551-2024 artfynd.xlsx
+++ b/artfynd/A 56551-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031523</v>
+        <v>122031485</v>
       </c>
       <c r="B2" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763364</v>
+        <v>763412</v>
       </c>
       <c r="R2" t="n">
-        <v>7300032</v>
+        <v>7299962</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031485</v>
+        <v>122031523</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763412</v>
+        <v>763364</v>
       </c>
       <c r="R3" t="n">
-        <v>7299962</v>
+        <v>7300032</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
